--- a/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-24T19:48:18+00:00</t>
+    <t>2024-10-29T08:42:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T08:42:45+00:00</t>
+    <t>2024-10-29T10:21:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T10:21:23+00:00</t>
+    <t>2024-10-29T14:54:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T14:54:01+00:00</t>
+    <t>2024-10-31T07:20:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31T07:20:54+00:00</t>
+    <t>2024-11-06T10:03:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T10:03:56+00:00</t>
+    <t>2024-11-06T10:30:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T10:30:49+00:00</t>
+    <t>2024-11-06T13:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T13:09:39+00:00</t>
+    <t>2024-11-06T14:31:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-11T09:21:50+00:00</t>
+    <t>2024-11-11T13:58:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T06:47:57+00:00</t>
+    <t>2024-11-12T08:54:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T08:54:48+00:00</t>
+    <t>2024-11-12T10:30:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T10:30:22+00:00</t>
+    <t>2024-11-12T12:40:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T12:40:22+00:00</t>
+    <t>2024-11-12T14:33:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T14:33:00+00:00</t>
+    <t>2024-11-12T14:36:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T14:36:04+00:00</t>
+    <t>2024-11-12T18:20:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T18:20:22+00:00</t>
+    <t>2024-11-12T18:30:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T18:30:34+00:00</t>
+    <t>2024-11-12T19:00:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T19:00:23+00:00</t>
+    <t>2024-11-12T19:16:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T19:16:24+00:00</t>
+    <t>2024-11-12T19:22:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T19:22:29+00:00</t>
+    <t>2024-11-14T14:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T14:59:39+00:00</t>
+    <t>2024-11-14T15:15:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T15:15:53+00:00</t>
+    <t>2024-11-15T07:51:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T07:51:28+00:00</t>
+    <t>2024-11-15T09:58:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T09:58:51+00:00</t>
+    <t>2024-11-15T11:02:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T11:02:30+00:00</t>
+    <t>2024-11-15T19:27:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T19:27:47+00:00</t>
+    <t>2024-11-15T20:19:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T20:19:59+00:00</t>
+    <t>2024-11-17T19:53:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T19:53:01+00:00</t>
+    <t>2024-11-17T20:11:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T20:11:24+00:00</t>
+    <t>2024-11-20T22:25:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-20T22:25:32+00:00</t>
+    <t>2024-11-22T08:03:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="50">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-22T08:03:54+00:00</t>
+    <t>2024-12-12T14:30:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -99,10 +99,64 @@
     <t>Concept</t>
   </si>
   <si>
-    <t>TBD</t>
-  </si>
-  <si>
-    <t>This ValueSet is work in progress.</t>
+    <t>Aufnahme-in-arbeit</t>
+  </si>
+  <si>
+    <t>Aufnahme in Arbeit</t>
+  </si>
+  <si>
+    <t>Aufnahme-freigeben</t>
+  </si>
+  <si>
+    <t>Aufnahme freigeben</t>
+  </si>
+  <si>
+    <t>SV-verarbeitet</t>
+  </si>
+  <si>
+    <t>SV verarbeitet</t>
+  </si>
+  <si>
+    <t>Entlassung-Aviso</t>
+  </si>
+  <si>
+    <t>Entlassung Aviso</t>
+  </si>
+  <si>
+    <t>Entlassung-vollständig</t>
+  </si>
+  <si>
+    <t>Entlassung vollständig</t>
+  </si>
+  <si>
+    <t>Vorläufige-Meldung</t>
+  </si>
+  <si>
+    <t>Vorläufige Meldung</t>
+  </si>
+  <si>
+    <t>LGF-Korrekturaufforderung</t>
+  </si>
+  <si>
+    <t>LGF Korrekturaufforderung</t>
+  </si>
+  <si>
+    <t>Vorlaeufige-Freigabe</t>
+  </si>
+  <si>
+    <t>Vorläufige Freigabe</t>
+  </si>
+  <si>
+    <t>Endgueltige-Meldung</t>
+  </si>
+  <si>
+    <t>Endgültige Meldung</t>
+  </si>
+  <si>
+    <t>Endgueltige-Freigabe</t>
+  </si>
+  <si>
+    <t>Endgültige Freigabe</t>
   </si>
   <si>
     <t>System URI</t>
@@ -370,7 +424,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -395,18 +449,90 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -57,19 +57,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-12T14:30:40+00:00</t>
+    <t>2024-12-13T08:39:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Example Publisher</t>
+    <t>ELGA</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>Example Publisher (http://example.org/example-publisher)</t>
+    <t>ELGA (https://www.elga.gv.at/)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-13T08:39:47+00:00</t>
+    <t>2025-01-07T14:12:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T14:12:01+00:00</t>
+    <t>2025-01-07T14:17:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T14:17:45+00:00</t>
+    <t>2025-01-14T08:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T08:01:21+00:00</t>
+    <t>2025-01-14T08:16:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T08:16:01+00:00</t>
+    <t>2025-02-07T07:07:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-07T07:07:15+00:00</t>
+    <t>2025-02-07T10:07:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-07T10:07:52+00:00</t>
+    <t>2025-02-10T08:30:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T08:30:06+00:00</t>
+    <t>2025-02-10T08:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T08:38:31+00:00</t>
+    <t>2025-02-11T11:17:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T11:17:52+00:00</t>
+    <t>2025-02-11T16:50:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T16:50:04+00:00</t>
+    <t>2025-02-13T14:21:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
